--- a/A/chrVIII:93774-140660_32_finemapping.xlsx
+++ b/A/chrVIII:93774-140660_32_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2787" uniqueCount="2787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2779" uniqueCount="2779">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -7631,19 +7631,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -7935,21 +7926,6 @@
   </si>
   <si>
     <t xml:space="preserve">ATP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -8811,48 +8787,42 @@
         <v>2535</v>
       </c>
       <c r="Z1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA1" t="s">
         <v>2536</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>2537</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>2538</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>2539</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>2540</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>2541</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>2542</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>2543</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>2544</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>2547</v>
+        <v>2544</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -8906,59 +8876,57 @@
         <v>113512</v>
       </c>
       <c r="U2" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="V2" t="n">
         <v>436471</v>
       </c>
       <c r="W2" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-0.489434424153711</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0578061014658072</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>2548</v>
       </c>
       <c r="AD2" t="s">
         <v>18</v>
       </c>
       <c r="AE2" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AH2" t="n">
+        <v>2548</v>
+      </c>
+      <c r="AF2" t="n">
         <v>3</v>
       </c>
-      <c r="AI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>2552</v>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>2549</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -9012,59 +8980,57 @@
         <v>113512</v>
       </c>
       <c r="U3" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="V3" t="n">
         <v>322342</v>
       </c>
       <c r="W3" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.511860291079409</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0689332382839916</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>2552</v>
       </c>
       <c r="AD3" t="s">
         <v>18</v>
       </c>
       <c r="AE3" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>2552</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="AI3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>2556</v>
+      <c r="AG3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>2553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>2557</v>
+        <v>2554</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -9118,62 +9084,60 @@
         <v>113512</v>
       </c>
       <c r="U4" t="s">
-        <v>2558</v>
+        <v>2555</v>
       </c>
       <c r="V4" t="n">
         <v>352414</v>
       </c>
       <c r="W4" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.236201092777534</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.0356781717458037</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>2556</v>
       </c>
       <c r="AD4" t="s">
         <v>18</v>
       </c>
       <c r="AE4" t="s">
-        <v>2559</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>2559</v>
-      </c>
-      <c r="AH4" t="n">
+        <v>2556</v>
+      </c>
+      <c r="AF4" t="n">
         <v>3</v>
       </c>
-      <c r="AI4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>2560</v>
+      <c r="AG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>2557</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="D5" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="E5" t="n">
         <v>100241</v>
@@ -9224,59 +9188,57 @@
         <v>110021</v>
       </c>
       <c r="U5" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
       <c r="V5" t="n">
         <v>1385176</v>
       </c>
       <c r="W5" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.340409662445476</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0505966926302075</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>2561</v>
       </c>
       <c r="AD5" t="s">
         <v>18</v>
       </c>
       <c r="AE5" t="s">
-        <v>2564</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>2564</v>
-      </c>
-      <c r="AH5" t="n">
+        <v>2561</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2</v>
       </c>
-      <c r="AI5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>2565</v>
+      <c r="AG5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>2562</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>2566</v>
+        <v>2563</v>
       </c>
       <c r="D6" t="s">
         <v>104</v>
@@ -9330,59 +9292,57 @@
         <v>121315</v>
       </c>
       <c r="U6" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
       <c r="V6" t="n">
         <v>720813</v>
       </c>
       <c r="W6" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.142619724270449</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.0264440976253112</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>2561</v>
       </c>
       <c r="AD6" t="s">
         <v>18</v>
       </c>
       <c r="AE6" t="s">
-        <v>2564</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>2564</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>2566</v>
+        <v>2561</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>2563</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>2567</v>
+        <v>2564</v>
       </c>
       <c r="D7" t="s">
         <v>104</v>
@@ -9436,27 +9396,31 @@
         <v>121315</v>
       </c>
       <c r="U7" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="V7" t="n">
         <v>526335</v>
       </c>
       <c r="W7" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-0.258096426116998</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0492403683226972</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>38</v>
       </c>
       <c r="AD7" t="s">
         <v>18</v>
@@ -9464,31 +9428,25 @@
       <c r="AE7" t="s">
         <v>38</v>
       </c>
-      <c r="AF7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>2569</v>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>2566</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>2570</v>
+        <v>2567</v>
       </c>
       <c r="D8" t="s">
         <v>104</v>
@@ -9542,59 +9500,57 @@
         <v>121315</v>
       </c>
       <c r="U8" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="V8" t="n">
         <v>409169</v>
       </c>
       <c r="W8" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.403360343715158</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0863456369395286</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>2569</v>
       </c>
       <c r="AD8" t="s">
         <v>18</v>
       </c>
       <c r="AE8" t="s">
-        <v>2572</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>2572</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>2573</v>
+        <v>2569</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>2570</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>2574</v>
+        <v>2571</v>
       </c>
       <c r="D9" t="s">
         <v>104</v>
@@ -9648,59 +9604,57 @@
         <v>121315</v>
       </c>
       <c r="U9" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
       <c r="V9" t="n">
         <v>1039150</v>
       </c>
       <c r="W9" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.457722890057128</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.106290470342827</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>2573</v>
       </c>
       <c r="AD9" t="s">
         <v>18</v>
       </c>
       <c r="AE9" t="s">
-        <v>2576</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>2576</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>2577</v>
+        <v>2573</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>2574</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>2578</v>
+        <v>2575</v>
       </c>
       <c r="D10" t="s">
         <v>104</v>
@@ -9754,59 +9708,57 @@
         <v>121315</v>
       </c>
       <c r="U10" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="V10" t="n">
         <v>1059531</v>
       </c>
       <c r="W10" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.0332135744064381</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.00892325087337551</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>2577</v>
       </c>
       <c r="AD10" t="s">
         <v>18</v>
       </c>
       <c r="AE10" t="s">
-        <v>2580</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>2580</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>2581</v>
+        <v>2577</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>2578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -9860,59 +9812,57 @@
         <v>113512</v>
       </c>
       <c r="U11" t="s">
-        <v>2558</v>
+        <v>2555</v>
       </c>
       <c r="V11" t="n">
         <v>703699</v>
       </c>
       <c r="W11" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.495426852698646</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.144915771274908</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>2556</v>
       </c>
       <c r="AD11" t="s">
         <v>18</v>
       </c>
       <c r="AE11" t="s">
-        <v>2559</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>2559</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>2583</v>
+        <v>2556</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>2580</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>2584</v>
+        <v>2581</v>
       </c>
       <c r="D12" t="s">
         <v>104</v>
@@ -9966,59 +9916,57 @@
         <v>121315</v>
       </c>
       <c r="U12" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
       <c r="V12" t="n">
         <v>42303</v>
       </c>
       <c r="W12" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z12" t="n">
         <v>-0.275355169867927</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0742571782908652</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>2583</v>
       </c>
       <c r="AD12" t="s">
         <v>18</v>
       </c>
       <c r="AE12" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>2587</v>
+        <v>2583</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -10072,62 +10020,60 @@
         <v>113512</v>
       </c>
       <c r="U13" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="V13" t="n">
         <v>1069501</v>
       </c>
       <c r="W13" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.249241747086701</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0713582083757667</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>2577</v>
       </c>
       <c r="AD13" t="s">
         <v>18</v>
       </c>
       <c r="AE13" t="s">
-        <v>2580</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>2580</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>2588</v>
+        <v>2577</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>2585</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="D14" t="s">
-        <v>2590</v>
+        <v>2587</v>
       </c>
       <c r="E14" t="n">
         <v>71885</v>
@@ -10178,59 +10124,57 @@
         <v>97536</v>
       </c>
       <c r="U14" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="V14" t="n">
         <v>1057455</v>
       </c>
       <c r="W14" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-0.050852871294068</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0156274241906382</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>2548</v>
       </c>
       <c r="AD14" t="s">
         <v>18</v>
       </c>
       <c r="AE14" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>2591</v>
+        <v>2548</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>2588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>2592</v>
+        <v>2589</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -10284,59 +10228,57 @@
         <v>113512</v>
       </c>
       <c r="U15" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="V15" t="n">
         <v>192451</v>
       </c>
       <c r="W15" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z15" t="n">
         <v>-0.237477421710318</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0769328267787183</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>2569</v>
       </c>
       <c r="AD15" t="s">
         <v>18</v>
       </c>
       <c r="AE15" t="s">
-        <v>2572</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>2572</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>2593</v>
+        <v>2569</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>2590</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>2594</v>
+        <v>2591</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -10390,62 +10332,60 @@
         <v>113512</v>
       </c>
       <c r="U16" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="V16" t="n">
         <v>162768</v>
       </c>
       <c r="W16" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-0.0972714966385063</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0311887022955605</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>2569</v>
       </c>
       <c r="AD16" t="s">
         <v>18</v>
       </c>
       <c r="AE16" t="s">
-        <v>2572</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>2572</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>2595</v>
+        <v>2569</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>2592</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>2596</v>
+        <v>2593</v>
       </c>
       <c r="D17" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="E17" t="n">
         <v>69672</v>
@@ -10496,62 +10436,60 @@
         <v>110021</v>
       </c>
       <c r="U17" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="V17" t="n">
         <v>205635</v>
       </c>
       <c r="W17" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-1.03423685064011</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.37163486389961</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>2552</v>
       </c>
       <c r="AD17" t="s">
         <v>18</v>
       </c>
       <c r="AE17" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>2596</v>
+        <v>2552</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>2593</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="D18" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E18" t="n">
         <v>97536</v>
@@ -10602,59 +10540,57 @@
         <v>108387</v>
       </c>
       <c r="U18" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
       <c r="V18" t="n">
         <v>229846</v>
       </c>
       <c r="W18" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z18" t="n">
         <v>-0.535092966685444</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.179727238428204</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>2573</v>
       </c>
       <c r="AD18" t="s">
         <v>18</v>
       </c>
       <c r="AE18" t="s">
-        <v>2576</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>2576</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>2597</v>
+        <v>2573</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>2594</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>2599</v>
+        <v>2596</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -10708,62 +10644,60 @@
         <v>113512</v>
       </c>
       <c r="U19" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="V19" t="n">
         <v>736926</v>
       </c>
       <c r="W19" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.676773566568159</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.234606060532396</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>2598</v>
       </c>
       <c r="AD19" t="s">
         <v>18</v>
       </c>
       <c r="AE19" t="s">
-        <v>2601</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>2601</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>2602</v>
+        <v>2598</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>2599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>2603</v>
+        <v>2600</v>
       </c>
       <c r="D20" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="E20" t="n">
         <v>110021</v>
@@ -10814,62 +10748,60 @@
         <v>122370</v>
       </c>
       <c r="U20" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="V20" t="n">
         <v>423961</v>
       </c>
       <c r="W20" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.106838197645508</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.035159886792754</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>2548</v>
       </c>
       <c r="AD20" t="s">
         <v>18</v>
       </c>
       <c r="AE20" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>2603</v>
+        <v>2548</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>2600</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>2605</v>
+        <v>2602</v>
       </c>
       <c r="D21" t="s">
-        <v>2590</v>
+        <v>2587</v>
       </c>
       <c r="E21" t="n">
         <v>74739</v>
@@ -10920,62 +10852,60 @@
         <v>97536</v>
       </c>
       <c r="U21" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="V21" t="n">
         <v>140493</v>
       </c>
       <c r="W21" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-0.192040774497167</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.0798332899214749</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>2552</v>
       </c>
       <c r="AD21" t="s">
         <v>18</v>
       </c>
       <c r="AE21" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>2606</v>
+        <v>2552</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>2603</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="D22" t="s">
-        <v>2608</v>
+        <v>2605</v>
       </c>
       <c r="E22" t="n">
         <v>108387</v>
@@ -11026,62 +10956,60 @@
         <v>129228</v>
       </c>
       <c r="U22" t="s">
-        <v>2609</v>
+        <v>2606</v>
       </c>
       <c r="V22" t="n">
         <v>378640</v>
       </c>
       <c r="W22" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z22" t="n">
         <v>-0.075511563230097</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0593023037486524</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>2607</v>
       </c>
       <c r="AD22" t="s">
         <v>18</v>
       </c>
       <c r="AE22" t="s">
-        <v>2610</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>2610</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>2607</v>
+      </c>
+      <c r="AF22" t="n">
         <v>4</v>
       </c>
-      <c r="AI22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>2611</v>
+      <c r="AG22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>2608</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>2612</v>
+        <v>2609</v>
       </c>
       <c r="D23" t="s">
-        <v>2613</v>
+        <v>2610</v>
       </c>
       <c r="E23" t="n">
         <v>74739</v>
@@ -11132,62 +11060,60 @@
         <v>102263</v>
       </c>
       <c r="U23" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="V23" t="n">
         <v>321454</v>
       </c>
       <c r="W23" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.0944526399004761</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0384622623562382</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>2552</v>
       </c>
       <c r="AD23" t="s">
         <v>18</v>
       </c>
       <c r="AE23" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>2614</v>
+        <v>2552</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>2611</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="D24" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="E24" t="n">
         <v>110021</v>
@@ -11238,59 +11164,57 @@
         <v>122370</v>
       </c>
       <c r="U24" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="V24" t="n">
         <v>878900</v>
       </c>
       <c r="W24" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z24" t="n">
         <v>-0.256385822757011</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.106667168309346</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>2598</v>
       </c>
       <c r="AD24" t="s">
         <v>18</v>
       </c>
       <c r="AE24" t="s">
-        <v>2601</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>2601</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>2616</v>
+        <v>2598</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>2613</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>2617</v>
+        <v>2614</v>
       </c>
       <c r="D25" t="s">
         <v>104</v>
@@ -11344,62 +11268,60 @@
         <v>121315</v>
       </c>
       <c r="U25" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
       <c r="V25" t="n">
         <v>658596</v>
       </c>
       <c r="W25" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z25" t="n">
         <v>-0.377795611408051</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.147562937031579</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>2583</v>
       </c>
       <c r="AD25" t="s">
         <v>18</v>
       </c>
       <c r="AE25" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>2618</v>
+        <v>2583</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>2615</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>2619</v>
+        <v>2616</v>
       </c>
       <c r="D26" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E26" t="n">
         <v>100241</v>
@@ -11450,62 +11372,60 @@
         <v>108387</v>
       </c>
       <c r="U26" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
       <c r="V26" t="n">
         <v>1292252</v>
       </c>
       <c r="W26" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z26" t="n">
         <v>-0.0871357052415555</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.0504528243209961</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>2561</v>
       </c>
       <c r="AD26" t="s">
         <v>18</v>
       </c>
       <c r="AE26" t="s">
-        <v>2564</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>2564</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>2620</v>
+        <v>2561</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>2617</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="D27" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="E27" t="n">
         <v>97536</v>
@@ -11556,62 +11476,60 @@
         <v>122370</v>
       </c>
       <c r="U27" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="V27" t="n">
         <v>878660</v>
       </c>
       <c r="W27" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z27" t="n">
         <v>-0.323512826438497</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.119333825676011</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>2598</v>
       </c>
       <c r="AD27" t="s">
         <v>18</v>
       </c>
       <c r="AE27" t="s">
-        <v>2601</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>2601</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>2621</v>
+        <v>2598</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>2618</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>2622</v>
+        <v>2619</v>
       </c>
       <c r="D28" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="E28" t="n">
         <v>83943</v>
@@ -11662,27 +11580,31 @@
         <v>110021</v>
       </c>
       <c r="U28" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="V28" t="n">
         <v>622474</v>
       </c>
       <c r="W28" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
       </c>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Y28" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.0269498750385547</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AA28" t="n">
         <v>0.0106858362786277</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>38</v>
       </c>
       <c r="AD28" t="s">
         <v>18</v>
@@ -11690,34 +11612,28 @@
       <c r="AE28" t="s">
         <v>38</v>
       </c>
-      <c r="AF28" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>2623</v>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>2620</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>2624</v>
+        <v>2621</v>
       </c>
       <c r="D29" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="E29" t="n">
         <v>67629</v>
@@ -11768,59 +11684,57 @@
         <v>122370</v>
       </c>
       <c r="U29" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="V29" t="n">
         <v>1060242</v>
       </c>
       <c r="W29" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="Y29" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.0337305115476999</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AA29" t="n">
         <v>0.01433993128361</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>2577</v>
       </c>
       <c r="AD29" t="s">
         <v>18</v>
       </c>
       <c r="AE29" t="s">
-        <v>2580</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>2580</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="s">
-        <v>2625</v>
+        <v>2577</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>2622</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>2626</v>
+        <v>2623</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -11874,62 +11788,60 @@
         <v>113512</v>
       </c>
       <c r="U30" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
       <c r="V30" t="n">
         <v>369891</v>
       </c>
       <c r="W30" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
       </c>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="Y30" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z30" t="n">
         <v>-0.0903749603954146</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AA30" t="n">
         <v>0.0409321237430239</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>2583</v>
       </c>
       <c r="AD30" t="s">
         <v>18</v>
       </c>
       <c r="AE30" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>2627</v>
+        <v>2583</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>2624</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>2628</v>
+        <v>2625</v>
       </c>
       <c r="D31" t="s">
-        <v>2629</v>
+        <v>2626</v>
       </c>
       <c r="E31" t="n">
         <v>108387</v>
@@ -11980,62 +11892,60 @@
         <v>130538</v>
       </c>
       <c r="U31" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="V31" t="n">
         <v>220138</v>
       </c>
       <c r="W31" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="Y31" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.0336149607043753</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AA31" t="n">
         <v>0.0156580626826701</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>2598</v>
       </c>
       <c r="AD31" t="s">
         <v>18</v>
       </c>
       <c r="AE31" t="s">
-        <v>2601</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>2601</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>2630</v>
+        <v>2598</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>2627</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>2631</v>
+        <v>2628</v>
       </c>
       <c r="D32" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="E32" t="n">
         <v>71885</v>
@@ -12086,59 +11996,57 @@
         <v>122370</v>
       </c>
       <c r="U32" t="s">
-        <v>2632</v>
+        <v>2629</v>
       </c>
       <c r="V32" t="n">
         <v>71683</v>
       </c>
       <c r="W32" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
       </c>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="Y32" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z32" t="n">
         <v>-0.578036048313849</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AA32" t="n">
         <v>0.230855729863354</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>2630</v>
       </c>
       <c r="AD32" t="s">
         <v>18</v>
       </c>
       <c r="AE32" t="s">
-        <v>2633</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>2633</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>2634</v>
+        <v>2630</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>2631</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>2635</v>
+        <v>2632</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
@@ -12192,48 +12100,46 @@
         <v>113512</v>
       </c>
       <c r="U33" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="V33" t="n">
         <v>37053</v>
       </c>
       <c r="W33" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
       </c>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33" t="s">
-        <v>2550</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="Y33" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Z33" t="n">
         <v>-0.0754816422077331</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AA33" t="n">
         <v>0.0316037680933714</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>2569</v>
       </c>
       <c r="AD33" t="s">
         <v>18</v>
       </c>
       <c r="AE33" t="s">
-        <v>2572</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>2572</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>2636</v>
+        <v>2569</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>2633</v>
       </c>
     </row>
   </sheetData>
@@ -12312,37 +12218,28 @@
         <v>2532</v>
       </c>
       <c r="V1" t="s">
-        <v>2637</v>
+        <v>116</v>
       </c>
       <c r="W1" t="s">
-        <v>2638</v>
+        <v>2536</v>
       </c>
       <c r="X1" t="s">
-        <v>2639</v>
+        <v>2537</v>
       </c>
       <c r="Y1" t="s">
-        <v>2640</v>
+        <v>2538</v>
       </c>
       <c r="Z1" t="s">
-        <v>2641</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="AB1" t="s">
-        <v>2541</v>
+        <v>2634</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>2542</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>2642</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="2">
@@ -12350,10 +12247,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>2643</v>
+        <v>2635</v>
       </c>
       <c r="C2" t="s">
-        <v>2644</v>
+        <v>2636</v>
       </c>
       <c r="D2" t="n">
         <v>74739</v>
@@ -12410,37 +12307,28 @@
         <v>75412</v>
       </c>
       <c r="V2" t="n">
-        <v>8.02477799244865</v>
+        <v>0.227802332410487</v>
       </c>
       <c r="W2" t="n">
-        <v>6.82268668733627</v>
-      </c>
-      <c r="X2" t="n">
-        <v>5.81437912201955</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>5.60143075543971</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7.36836005425925</v>
+        <v>0.0333125864904957</v>
+      </c>
+      <c r="X2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>18</v>
       </c>
       <c r="AA2" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" t="s">
-        <v>18</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>2645</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="3">
@@ -12451,7 +12339,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="D3" t="n">
         <v>121315</v>
@@ -12508,36 +12396,27 @@
         <v>119825</v>
       </c>
       <c r="V3" t="n">
-        <v>10.9095664818262</v>
+        <v>0.272338851064543</v>
       </c>
       <c r="W3" t="n">
-        <v>5.43913660674817</v>
-      </c>
-      <c r="X3" t="n">
-        <v>5.79402115258942</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.98094197370003</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.63656793047124</v>
+        <v>0.041253683287147</v>
+      </c>
+      <c r="X3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>18</v>
       </c>
       <c r="AA3" t="s">
         <v>18</v>
       </c>
-      <c r="AB3" t="s">
-        <v>18</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
         <v>93</v>
       </c>
     </row>
@@ -12546,10 +12425,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>2646</v>
+        <v>2638</v>
       </c>
       <c r="C4" t="s">
-        <v>2647</v>
+        <v>2639</v>
       </c>
       <c r="D4" t="n">
         <v>80498</v>
@@ -12606,37 +12485,28 @@
         <v>100413</v>
       </c>
       <c r="V4" t="n">
-        <v>-6.81670538881356</v>
+        <v>-0.274708803054774</v>
       </c>
       <c r="W4" t="n">
-        <v>-4.58353066663384</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-5.15592753882314</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-4.69964236235087</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-7.07867961848994</v>
+        <v>0.0477250102545324</v>
+      </c>
+      <c r="X4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>18</v>
       </c>
       <c r="AA4" t="s">
         <v>18</v>
       </c>
-      <c r="AB4" t="s">
-        <v>18</v>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>2648</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="5">
@@ -12644,10 +12514,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>2649</v>
+        <v>2641</v>
       </c>
       <c r="C5" t="s">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="D5" t="n">
         <v>100241</v>
@@ -12704,37 +12574,28 @@
         <v>99219</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.35403056998025</v>
+        <v>-0.401610674526335</v>
       </c>
       <c r="W5" t="n">
-        <v>-5.26346029605202</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-4.18831086346013</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-2.84484812306422</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-5.72735991460925</v>
+        <v>0.0948634375176784</v>
+      </c>
+      <c r="X5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>18</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>
       </c>
-      <c r="AB5" t="s">
-        <v>18</v>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>2651</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="6">
@@ -12742,7 +12603,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>2652</v>
+        <v>2644</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -12802,37 +12663,28 @@
         <v>113379</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.05732175997977</v>
+        <v>-0.192713501194432</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.14653941060138</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-4.63578628623931</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.58660762483916</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-1.16756473826898</v>
+        <v>0.0490524941286191</v>
+      </c>
+      <c r="X6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>18</v>
       </c>
       <c r="AA6" t="s">
         <v>18</v>
       </c>
-      <c r="AB6" t="s">
-        <v>18</v>
+      <c r="AB6" t="n">
+        <v>0</v>
       </c>
       <c r="AC6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>2653</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="7">
@@ -12840,10 +12692,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>2654</v>
+        <v>2646</v>
       </c>
       <c r="C7" t="s">
-        <v>2655</v>
+        <v>2647</v>
       </c>
       <c r="D7" t="n">
         <v>125040</v>
@@ -12900,37 +12752,28 @@
         <v>123987</v>
       </c>
       <c r="V7" t="n">
-        <v>6.07469940254822</v>
+        <v>0.244489360126571</v>
       </c>
       <c r="W7" t="n">
-        <v>4.26188344633715</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.78360578465925</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>4.14076208103506</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.257402584982465</v>
+        <v>0.0692900764237835</v>
+      </c>
+      <c r="X7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>18</v>
       </c>
       <c r="AA7" t="s">
         <v>18</v>
       </c>
-      <c r="AB7" t="s">
-        <v>18</v>
+      <c r="AB7" t="n">
+        <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>2656</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="8">
@@ -12938,7 +12781,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>2657</v>
+        <v>2649</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -12998,37 +12841,28 @@
         <v>111634</v>
       </c>
       <c r="V8" t="n">
-        <v>4.67188953461704</v>
+        <v>0.417500468327919</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9157803120187</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.29361489943148</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3.8243966459963</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.63254282468677</v>
+        <v>0.12571438911425</v>
+      </c>
+      <c r="X8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>18</v>
       </c>
       <c r="AA8" t="s">
         <v>18</v>
       </c>
-      <c r="AB8" t="s">
-        <v>18</v>
+      <c r="AB8" t="n">
+        <v>0</v>
       </c>
       <c r="AC8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>2658</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="9">
@@ -13036,10 +12870,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>2659</v>
+        <v>2651</v>
       </c>
       <c r="C9" t="s">
-        <v>2660</v>
+        <v>2652</v>
       </c>
       <c r="D9" t="n">
         <v>68955</v>
@@ -13096,37 +12930,28 @@
         <v>71917</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.69771807090669</v>
+        <v>-0.598751788635442</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.15240955629386</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.9663520339018</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-3.18675825445997</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-3.46560988222554</v>
+        <v>0.191594536504321</v>
+      </c>
+      <c r="X9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>18</v>
       </c>
       <c r="AA9" t="s">
         <v>18</v>
       </c>
-      <c r="AB9" t="s">
-        <v>18</v>
+      <c r="AB9" t="n">
+        <v>0</v>
       </c>
       <c r="AC9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>2661</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="10">
@@ -13134,10 +12959,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>2662</v>
+        <v>2654</v>
       </c>
       <c r="C10" t="s">
-        <v>2663</v>
+        <v>2655</v>
       </c>
       <c r="D10" t="n">
         <v>142368</v>
@@ -13194,37 +13019,28 @@
         <v>106055</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29382368401755</v>
+        <v>0.114928212755442</v>
       </c>
       <c r="W10" t="n">
-        <v>2.25764524077193</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03420022801538</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.88190570886798</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.63565112193477</v>
+        <v>0.0586116285983899</v>
+      </c>
+      <c r="X10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>18</v>
       </c>
       <c r="AA10" t="s">
         <v>18</v>
       </c>
-      <c r="AB10" t="s">
-        <v>18</v>
+      <c r="AB10" t="n">
+        <v>0.00179910044977511</v>
       </c>
       <c r="AC10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.00179910044977511</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>2664</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="11">
@@ -13232,10 +13048,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>2665</v>
+        <v>2657</v>
       </c>
       <c r="C11" t="s">
-        <v>2666</v>
+        <v>2658</v>
       </c>
       <c r="D11" t="n">
         <v>67629</v>
@@ -13292,37 +13108,28 @@
         <v>98223</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2575023196538</v>
+        <v>-0.146374536654166</v>
       </c>
       <c r="W11" t="n">
-        <v>2.84360467282819</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.333058084289678</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.547480706789574</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-2.26895808317954</v>
+        <v>0.291482486536832</v>
+      </c>
+      <c r="X11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>18</v>
       </c>
       <c r="AA11" t="s">
         <v>18</v>
       </c>
-      <c r="AB11" t="s">
-        <v>18</v>
+      <c r="AB11" t="n">
+        <v>0.0235698486613298</v>
       </c>
       <c r="AC11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.0235698486613298</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="12">
@@ -13330,10 +13137,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="C12" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="D12" t="n">
         <v>175734</v>
@@ -13390,37 +13197,28 @@
         <v>70276</v>
       </c>
       <c r="V12" t="n">
-        <v>2.53242095762145</v>
+        <v>-0.0298675958013791</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.06019035567096</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-2.53307831856062</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-0.142685247884935</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-1.43306509558463</v>
+        <v>0.0898193744035078</v>
+      </c>
+      <c r="X12" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>18</v>
       </c>
       <c r="AA12" t="s">
         <v>18</v>
       </c>
-      <c r="AB12" t="s">
-        <v>18</v>
+      <c r="AB12" t="n">
+        <v>0.0283226705751171</v>
       </c>
       <c r="AC12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.0283226705751171</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="13">
@@ -13428,10 +13226,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>2670</v>
+        <v>2662</v>
       </c>
       <c r="C13" t="s">
-        <v>2671</v>
+        <v>2663</v>
       </c>
       <c r="D13" t="n">
         <v>164380</v>
@@ -13488,37 +13286,28 @@
         <v>94998</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.67525930898034</v>
+        <v>-0.0278535630141513</v>
       </c>
       <c r="W13" t="n">
-        <v>0.916278903597953</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-1.68037878982895</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.954870576348599</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.77310609735077</v>
+        <v>0.0835417977617136</v>
+      </c>
+      <c r="X13" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>18</v>
       </c>
       <c r="AA13" t="s">
         <v>18</v>
       </c>
-      <c r="AB13" t="s">
-        <v>18</v>
+      <c r="AB13" t="n">
+        <v>0.0450789534799948</v>
       </c>
       <c r="AC13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.0450789534799948</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>2672</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="14">
@@ -13526,10 +13315,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="C14" t="s">
-        <v>2674</v>
+        <v>2666</v>
       </c>
       <c r="D14" t="n">
         <v>27988</v>
@@ -13586,37 +13375,28 @@
         <v>108812</v>
       </c>
       <c r="V14" t="n">
-        <v>2.92107825381067</v>
+        <v>0.0703061400057635</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.97489634767699</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.10065135774053</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.925729955066909</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-0.118092444516581</v>
+        <v>0.112000961678486</v>
+      </c>
+      <c r="X14" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>18</v>
       </c>
       <c r="AA14" t="s">
         <v>18</v>
       </c>
-      <c r="AB14" t="s">
-        <v>18</v>
+      <c r="AB14" t="n">
+        <v>0.0494870282832931</v>
       </c>
       <c r="AC14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.0494870282832931</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
     </row>
   </sheetData>
@@ -13647,34 +13427,34 @@
         <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>2676</v>
+        <v>2668</v>
       </c>
       <c r="G1" t="s">
         <v>1054</v>
       </c>
       <c r="H1" t="s">
-        <v>2677</v>
+        <v>2669</v>
       </c>
       <c r="I1" t="s">
-        <v>2678</v>
+        <v>2670</v>
       </c>
       <c r="J1" t="s">
         <v>1072</v>
       </c>
       <c r="K1" t="s">
-        <v>2679</v>
+        <v>2671</v>
       </c>
       <c r="L1" t="s">
-        <v>2680</v>
+        <v>2672</v>
       </c>
       <c r="M1" t="s">
-        <v>2681</v>
+        <v>2673</v>
       </c>
       <c r="N1" t="s">
-        <v>2682</v>
+        <v>2674</v>
       </c>
       <c r="O1" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="P1" t="s">
         <v>2532</v>
@@ -13694,33 +13474,33 @@
         <v>1818</v>
       </c>
       <c r="E2" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F2" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G2" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>2686</v>
+        <v>2678</v>
       </c>
       <c r="K2" t="s">
-        <v>2687</v>
+        <v>2679</v>
       </c>
       <c r="L2" t="s">
-        <v>2686</v>
+        <v>2678</v>
       </c>
       <c r="M2" t="s">
-        <v>2688</v>
+        <v>2680</v>
       </c>
       <c r="N2" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O2" t="s">
-        <v>2690</v>
+        <v>2682</v>
       </c>
       <c r="P2" t="n">
         <v>68640</v>
@@ -13740,30 +13520,30 @@
         <v>363</v>
       </c>
       <c r="E3" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F3" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G3" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>2692</v>
+        <v>2684</v>
       </c>
       <c r="K3" t="s">
-        <v>2693</v>
+        <v>2685</v>
       </c>
       <c r="L3" t="s">
-        <v>2692</v>
+        <v>2684</v>
       </c>
       <c r="M3" t="s">
-        <v>2694</v>
+        <v>2686</v>
       </c>
       <c r="N3" t="s">
-        <v>2695</v>
+        <v>2687</v>
       </c>
       <c r="O3"/>
       <c r="P3" t="n">
@@ -13784,30 +13564,30 @@
         <v>1599</v>
       </c>
       <c r="E4" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F4" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G4" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="K4" t="s">
-        <v>2696</v>
+        <v>2688</v>
       </c>
       <c r="L4" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="M4" t="s">
-        <v>2697</v>
+        <v>2689</v>
       </c>
       <c r="N4" t="s">
-        <v>2695</v>
+        <v>2687</v>
       </c>
       <c r="O4"/>
       <c r="P4" t="n">
@@ -13828,33 +13608,33 @@
         <v>2208</v>
       </c>
       <c r="E5" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F5" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G5" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>2659</v>
+        <v>2651</v>
       </c>
       <c r="K5" t="s">
-        <v>2698</v>
+        <v>2690</v>
       </c>
       <c r="L5" t="s">
-        <v>2659</v>
+        <v>2651</v>
       </c>
       <c r="M5" t="s">
-        <v>2699</v>
+        <v>2691</v>
       </c>
       <c r="N5" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O5" t="s">
-        <v>2661</v>
+        <v>2653</v>
       </c>
       <c r="P5" t="n">
         <v>73140</v>
@@ -13874,30 +13654,30 @@
         <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F6" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G6" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>2700</v>
+        <v>2692</v>
       </c>
       <c r="K6" t="s">
-        <v>2701</v>
+        <v>2693</v>
       </c>
       <c r="L6" t="s">
-        <v>2700</v>
+        <v>2692</v>
       </c>
       <c r="M6" t="s">
-        <v>2697</v>
+        <v>2689</v>
       </c>
       <c r="N6" t="s">
-        <v>2695</v>
+        <v>2687</v>
       </c>
       <c r="O6"/>
       <c r="P6" t="n">
@@ -13918,33 +13698,33 @@
         <v>366</v>
       </c>
       <c r="E7" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F7" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G7" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>2643</v>
+        <v>2635</v>
       </c>
       <c r="K7" t="s">
-        <v>2702</v>
+        <v>2694</v>
       </c>
       <c r="L7" t="s">
-        <v>2643</v>
+        <v>2635</v>
       </c>
       <c r="M7" t="s">
-        <v>2703</v>
+        <v>2695</v>
       </c>
       <c r="N7" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O7" t="s">
-        <v>2645</v>
+        <v>2637</v>
       </c>
       <c r="P7" t="n">
         <v>75594</v>
@@ -13964,33 +13744,33 @@
         <v>1218</v>
       </c>
       <c r="E8" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F8" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G8" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>2704</v>
+        <v>2696</v>
       </c>
       <c r="K8" t="s">
-        <v>2705</v>
+        <v>2697</v>
       </c>
       <c r="L8" t="s">
-        <v>2704</v>
+        <v>2696</v>
       </c>
       <c r="M8" t="s">
-        <v>2688</v>
+        <v>2680</v>
       </c>
       <c r="N8" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O8" t="s">
-        <v>2706</v>
+        <v>2698</v>
       </c>
       <c r="P8" t="n">
         <v>76706</v>
@@ -14010,33 +13790,33 @@
         <v>924</v>
       </c>
       <c r="E9" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F9" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G9" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>2707</v>
+        <v>2699</v>
       </c>
       <c r="K9" t="s">
-        <v>2708</v>
+        <v>2700</v>
       </c>
       <c r="L9" t="s">
-        <v>2707</v>
+        <v>2699</v>
       </c>
       <c r="M9" t="s">
-        <v>2688</v>
+        <v>2680</v>
       </c>
       <c r="N9" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O9" t="s">
-        <v>2709</v>
+        <v>2701</v>
       </c>
       <c r="P9" t="n">
         <v>77892</v>
@@ -14056,30 +13836,30 @@
         <v>1482</v>
       </c>
       <c r="E10" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F10" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G10" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>2710</v>
+        <v>2702</v>
       </c>
       <c r="K10" t="s">
-        <v>2711</v>
+        <v>2703</v>
       </c>
       <c r="L10" t="s">
-        <v>2710</v>
+        <v>2702</v>
       </c>
       <c r="M10" t="s">
-        <v>2712</v>
+        <v>2704</v>
       </c>
       <c r="N10" t="s">
-        <v>2695</v>
+        <v>2687</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
@@ -14100,33 +13880,33 @@
         <v>963</v>
       </c>
       <c r="E11" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F11" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G11" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>2713</v>
+        <v>2705</v>
       </c>
       <c r="K11" t="s">
-        <v>2714</v>
+        <v>2706</v>
       </c>
       <c r="L11" t="s">
-        <v>2713</v>
+        <v>2705</v>
       </c>
       <c r="M11" t="s">
-        <v>2715</v>
+        <v>2707</v>
       </c>
       <c r="N11" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O11" t="s">
-        <v>2716</v>
+        <v>2708</v>
       </c>
       <c r="P11" t="n">
         <v>81135</v>
@@ -14146,33 +13926,33 @@
         <v>1758</v>
       </c>
       <c r="E12" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F12" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G12" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>2717</v>
+        <v>2709</v>
       </c>
       <c r="K12" t="s">
-        <v>2718</v>
+        <v>2710</v>
       </c>
       <c r="L12" t="s">
-        <v>2717</v>
+        <v>2709</v>
       </c>
       <c r="M12" t="s">
-        <v>2719</v>
+        <v>2711</v>
       </c>
       <c r="N12" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O12" t="s">
-        <v>2720</v>
+        <v>2712</v>
       </c>
       <c r="P12" t="n">
         <v>82842</v>
@@ -14192,33 +13972,33 @@
         <v>993</v>
       </c>
       <c r="E13" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F13" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G13" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>2721</v>
+        <v>2713</v>
       </c>
       <c r="K13" t="s">
-        <v>2722</v>
+        <v>2714</v>
       </c>
       <c r="L13" t="s">
-        <v>2721</v>
+        <v>2713</v>
       </c>
       <c r="M13" t="s">
-        <v>2723</v>
+        <v>2715</v>
       </c>
       <c r="N13" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O13" t="s">
-        <v>2724</v>
+        <v>2716</v>
       </c>
       <c r="P13" t="n">
         <v>84564</v>
@@ -14238,30 +14018,30 @@
         <v>1884</v>
       </c>
       <c r="E14" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F14" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G14" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>2725</v>
+        <v>2717</v>
       </c>
       <c r="K14" t="s">
-        <v>2726</v>
+        <v>2718</v>
       </c>
       <c r="L14" t="s">
-        <v>2725</v>
+        <v>2717</v>
       </c>
       <c r="M14" t="s">
-        <v>2697</v>
+        <v>2689</v>
       </c>
       <c r="N14" t="s">
-        <v>2695</v>
+        <v>2687</v>
       </c>
       <c r="O14"/>
       <c r="P14" t="n">
@@ -14282,33 +14062,33 @@
         <v>2820</v>
       </c>
       <c r="E15" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F15" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G15" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>2670</v>
+        <v>2662</v>
       </c>
       <c r="K15" t="s">
-        <v>2727</v>
+        <v>2719</v>
       </c>
       <c r="L15" t="s">
-        <v>2670</v>
+        <v>2662</v>
       </c>
       <c r="M15" t="s">
-        <v>2728</v>
+        <v>2720</v>
       </c>
       <c r="N15" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O15" t="s">
-        <v>2672</v>
+        <v>2664</v>
       </c>
       <c r="P15" t="n">
         <v>96528</v>
@@ -14328,33 +14108,33 @@
         <v>453</v>
       </c>
       <c r="E16" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F16" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G16" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>2665</v>
+        <v>2657</v>
       </c>
       <c r="K16" t="s">
-        <v>2729</v>
+        <v>2721</v>
       </c>
       <c r="L16" t="s">
-        <v>2665</v>
+        <v>2657</v>
       </c>
       <c r="M16" t="s">
-        <v>2730</v>
+        <v>2722</v>
       </c>
       <c r="N16" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O16" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="P16" t="n">
         <v>98569</v>
@@ -14374,30 +14154,30 @@
         <v>393</v>
       </c>
       <c r="E17" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F17" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G17" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>2731</v>
+        <v>2723</v>
       </c>
       <c r="K17" t="s">
-        <v>2732</v>
+        <v>2724</v>
       </c>
       <c r="L17" t="s">
-        <v>2731</v>
+        <v>2723</v>
       </c>
       <c r="M17" t="s">
-        <v>2697</v>
+        <v>2689</v>
       </c>
       <c r="N17" t="s">
-        <v>2695</v>
+        <v>2687</v>
       </c>
       <c r="O17"/>
       <c r="P17" t="n">
@@ -14418,33 +14198,33 @@
         <v>1185</v>
       </c>
       <c r="E18" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F18" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G18" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>2649</v>
+        <v>2641</v>
       </c>
       <c r="K18" t="s">
-        <v>2733</v>
+        <v>2725</v>
       </c>
       <c r="L18" t="s">
-        <v>2649</v>
+        <v>2641</v>
       </c>
       <c r="M18" t="s">
-        <v>2734</v>
+        <v>2726</v>
       </c>
       <c r="N18" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O18" t="s">
-        <v>2651</v>
+        <v>2643</v>
       </c>
       <c r="P18" t="n">
         <v>99811</v>
@@ -14464,33 +14244,33 @@
         <v>1236</v>
       </c>
       <c r="E19" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F19" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G19" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>2646</v>
+        <v>2638</v>
       </c>
       <c r="K19" t="s">
-        <v>2735</v>
+        <v>2727</v>
       </c>
       <c r="L19" t="s">
-        <v>2646</v>
+        <v>2638</v>
       </c>
       <c r="M19" t="s">
-        <v>2736</v>
+        <v>2728</v>
       </c>
       <c r="N19" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O19" t="s">
-        <v>2648</v>
+        <v>2640</v>
       </c>
       <c r="P19" t="n">
         <v>101266</v>
@@ -14510,33 +14290,33 @@
         <v>1359</v>
       </c>
       <c r="E20" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F20" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G20" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>2737</v>
+        <v>2729</v>
       </c>
       <c r="K20" t="s">
-        <v>2738</v>
+        <v>2730</v>
       </c>
       <c r="L20" t="s">
-        <v>2737</v>
+        <v>2729</v>
       </c>
       <c r="M20" t="s">
-        <v>2739</v>
+        <v>2731</v>
       </c>
       <c r="N20" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O20" t="s">
-        <v>2740</v>
+        <v>2732</v>
       </c>
       <c r="P20" t="n">
         <v>103291</v>
@@ -14556,33 +14336,33 @@
         <v>815</v>
       </c>
       <c r="E21" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F21" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G21" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>2741</v>
+        <v>2733</v>
       </c>
       <c r="K21" t="s">
-        <v>2742</v>
+        <v>2734</v>
       </c>
       <c r="L21" t="s">
-        <v>2741</v>
+        <v>2733</v>
       </c>
       <c r="M21" t="s">
-        <v>2743</v>
+        <v>2735</v>
       </c>
       <c r="N21" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O21" t="s">
-        <v>2744</v>
+        <v>2736</v>
       </c>
       <c r="P21" t="n">
         <v>104684</v>
@@ -14602,33 +14382,33 @@
         <v>1314</v>
       </c>
       <c r="E22" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F22" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G22" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>2662</v>
+        <v>2654</v>
       </c>
       <c r="K22" t="s">
-        <v>2745</v>
+        <v>2737</v>
       </c>
       <c r="L22" t="s">
-        <v>2662</v>
+        <v>2654</v>
       </c>
       <c r="M22" t="s">
-        <v>2746</v>
+        <v>2738</v>
       </c>
       <c r="N22" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O22" t="s">
-        <v>2664</v>
+        <v>2656</v>
       </c>
       <c r="P22" t="n">
         <v>106712</v>
@@ -14648,33 +14428,33 @@
         <v>297</v>
       </c>
       <c r="E23" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F23" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G23" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>2747</v>
+        <v>2739</v>
       </c>
       <c r="K23" t="s">
-        <v>2748</v>
+        <v>2740</v>
       </c>
       <c r="L23" t="s">
-        <v>2747</v>
+        <v>2739</v>
       </c>
       <c r="M23" t="s">
-        <v>2749</v>
+        <v>2741</v>
       </c>
       <c r="N23" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O23" t="s">
-        <v>2750</v>
+        <v>2742</v>
       </c>
       <c r="P23" t="n">
         <v>107974</v>
@@ -14694,33 +14474,33 @@
         <v>1074</v>
       </c>
       <c r="E24" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F24" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G24" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="K24" t="s">
-        <v>2751</v>
+        <v>2743</v>
       </c>
       <c r="L24" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="M24" t="s">
-        <v>2752</v>
+        <v>2744</v>
       </c>
       <c r="N24" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O24" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="P24" t="n">
         <v>109348</v>
@@ -14740,33 +14520,33 @@
         <v>1290</v>
       </c>
       <c r="E25" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F25" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G25" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>2753</v>
+        <v>2745</v>
       </c>
       <c r="K25" t="s">
-        <v>2754</v>
+        <v>2746</v>
       </c>
       <c r="L25" t="s">
-        <v>2753</v>
+        <v>2745</v>
       </c>
       <c r="M25" t="s">
-        <v>2755</v>
+        <v>2747</v>
       </c>
       <c r="N25" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O25" t="s">
-        <v>2756</v>
+        <v>2748</v>
       </c>
       <c r="P25" t="n">
         <v>110672</v>
@@ -14786,33 +14566,33 @@
         <v>1341</v>
       </c>
       <c r="E26" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F26" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G26" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>2657</v>
+        <v>2649</v>
       </c>
       <c r="K26" t="s">
-        <v>2757</v>
+        <v>2749</v>
       </c>
       <c r="L26" t="s">
-        <v>2657</v>
+        <v>2649</v>
       </c>
       <c r="M26" t="s">
-        <v>2758</v>
+        <v>2750</v>
       </c>
       <c r="N26" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O26" t="s">
-        <v>2658</v>
+        <v>2650</v>
       </c>
       <c r="P26" t="n">
         <v>112424</v>
@@ -14832,33 +14612,33 @@
         <v>1419</v>
       </c>
       <c r="E27" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F27" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G27" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>2652</v>
+        <v>2644</v>
       </c>
       <c r="K27" t="s">
-        <v>2759</v>
+        <v>2751</v>
       </c>
       <c r="L27" t="s">
-        <v>2652</v>
+        <v>2644</v>
       </c>
       <c r="M27" t="s">
-        <v>2760</v>
+        <v>2752</v>
       </c>
       <c r="N27" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O27" t="s">
-        <v>2653</v>
+        <v>2645</v>
       </c>
       <c r="P27" t="n">
         <v>114208</v>
@@ -14878,33 +14658,33 @@
         <v>282</v>
       </c>
       <c r="E28" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F28" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G28" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>2761</v>
+        <v>2753</v>
       </c>
       <c r="K28" t="s">
-        <v>2762</v>
+        <v>2754</v>
       </c>
       <c r="L28" t="s">
-        <v>2761</v>
+        <v>2753</v>
       </c>
       <c r="M28" t="s">
-        <v>2763</v>
+        <v>2755</v>
       </c>
       <c r="N28" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O28" t="s">
-        <v>2764</v>
+        <v>2756</v>
       </c>
       <c r="P28" t="n">
         <v>115760</v>
@@ -14924,33 +14704,33 @@
         <v>1626</v>
       </c>
       <c r="E29" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F29" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G29" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>2765</v>
+        <v>2757</v>
       </c>
       <c r="K29" t="s">
-        <v>2766</v>
+        <v>2758</v>
       </c>
       <c r="L29" t="s">
-        <v>2765</v>
+        <v>2757</v>
       </c>
       <c r="M29" t="s">
-        <v>2767</v>
+        <v>2759</v>
       </c>
       <c r="N29" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O29" t="s">
-        <v>2768</v>
+        <v>2760</v>
       </c>
       <c r="P29" t="n">
         <v>118626</v>
@@ -14970,13 +14750,13 @@
         <v>1593</v>
       </c>
       <c r="E30" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F30" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G30" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
@@ -14984,16 +14764,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s">
-        <v>2769</v>
+        <v>2761</v>
       </c>
       <c r="L30" t="s">
         <v>92</v>
       </c>
       <c r="M30" t="s">
-        <v>2770</v>
+        <v>2762</v>
       </c>
       <c r="N30" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O30" t="s">
         <v>93</v>
@@ -15016,30 +14796,30 @@
         <v>216</v>
       </c>
       <c r="E31" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F31" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G31" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>2771</v>
+        <v>2763</v>
       </c>
       <c r="K31" t="s">
-        <v>2772</v>
+        <v>2764</v>
       </c>
       <c r="L31" t="s">
-        <v>2771</v>
+        <v>2763</v>
       </c>
       <c r="M31" t="s">
-        <v>2697</v>
+        <v>2689</v>
       </c>
       <c r="N31" t="s">
-        <v>2695</v>
+        <v>2687</v>
       </c>
       <c r="O31"/>
       <c r="P31" t="n">
@@ -15060,33 +14840,33 @@
         <v>702</v>
       </c>
       <c r="E32" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F32" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G32" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>2773</v>
+        <v>2765</v>
       </c>
       <c r="K32" t="s">
-        <v>2774</v>
+        <v>2766</v>
       </c>
       <c r="L32" t="s">
-        <v>2773</v>
+        <v>2765</v>
       </c>
       <c r="M32" t="s">
-        <v>2775</v>
+        <v>2767</v>
       </c>
       <c r="N32" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O32" t="s">
-        <v>2776</v>
+        <v>2768</v>
       </c>
       <c r="P32" t="n">
         <v>123240</v>
@@ -15106,33 +14886,33 @@
         <v>1572</v>
       </c>
       <c r="E33" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="F33" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G33" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>2654</v>
+        <v>2646</v>
       </c>
       <c r="K33" t="s">
-        <v>2777</v>
+        <v>2769</v>
       </c>
       <c r="L33" t="s">
-        <v>2654</v>
+        <v>2646</v>
       </c>
       <c r="M33" t="s">
-        <v>2778</v>
+        <v>2770</v>
       </c>
       <c r="N33" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O33" t="s">
-        <v>2656</v>
+        <v>2648</v>
       </c>
       <c r="P33" t="n">
         <v>124894</v>
@@ -15152,33 +14932,33 @@
         <v>972</v>
       </c>
       <c r="E34" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F34" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G34" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>2779</v>
+        <v>2771</v>
       </c>
       <c r="K34" t="s">
-        <v>2780</v>
+        <v>2772</v>
       </c>
       <c r="L34" t="s">
-        <v>2779</v>
+        <v>2771</v>
       </c>
       <c r="M34" t="s">
-        <v>2781</v>
+        <v>2773</v>
       </c>
       <c r="N34" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O34" t="s">
-        <v>2782</v>
+        <v>2774</v>
       </c>
       <c r="P34" t="n">
         <v>127006</v>
@@ -15198,33 +14978,33 @@
         <v>1341</v>
       </c>
       <c r="E35" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="F35" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="G35" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>2783</v>
+        <v>2775</v>
       </c>
       <c r="K35" t="s">
-        <v>2784</v>
+        <v>2776</v>
       </c>
       <c r="L35" t="s">
-        <v>2783</v>
+        <v>2775</v>
       </c>
       <c r="M35" t="s">
-        <v>2785</v>
+        <v>2777</v>
       </c>
       <c r="N35" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="O35" t="s">
-        <v>2786</v>
+        <v>2778</v>
       </c>
       <c r="P35" t="n">
         <v>128450</v>
